--- a/hira_material_automation/output/monthly/202601_202610__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202610__arthroscopy_cannula__041001__normalized.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:23</t>
+          <t>2026-10-14T23:46:55</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7a9b07a8afe0e6742ce40fc49ad40f28123e6a813f1be25c0bdf4b138906cd73</t>
+          <t>7955fd72a708fbfc8d6c73313c7c8527b6fb165c1e12569e23db16ccb3f07e44</t>
         </is>
       </c>
     </row>
